--- a/upload/baselegal_reducaoaliquota.xlsx
+++ b/upload/baselegal_reducaoaliquota.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>Norma</t>
   </si>
@@ -181,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -211,15 +211,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -456,94 +447,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -829,66 +814,74 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:3" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="C2" s="14"/>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="15"/>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="16" t="s">
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="17"/>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="16" t="s">
+      <c r="C4" s="18"/>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="17"/>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="16" t="s">
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="18" t="s">
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="19"/>
+      <c r="C7" s="20"/>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="21" t="s">
@@ -897,49 +890,51 @@
       <c r="C8" s="22"/>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="23"/>
+      <c r="C9" s="24"/>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="24"/>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="C10" s="26"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="29" t="s">
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -953,11 +948,9 @@
     <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A11:A13"/>
+  <mergeCells count="10">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="A3:A7"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
